--- a/pensum/ma06/MA06_Produkt_Regneark_Produktbidrag_og_sortiment.xlsx
+++ b/pensum/ma06/MA06_Produkt_Regneark_Produktbidrag_og_sortiment.xlsx
@@ -948,7 +948,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1107,6 +1107,10 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1731,11 +1735,11 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="23" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c s="40" r="B23" t="s">
         <v>59</v>
       </c>
       <c r="C23" s="19" t="s">
@@ -1763,8 +1767,8 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A28" t="s">
         <v>66</v>
       </c>
       <c r="B28" s="21" t="s">
@@ -1895,8 +1899,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+    <row ht="27" customHeight="true" r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A4" t="s">
         <v>87</v>
       </c>
       <c r="B4" s="23" t="n">
@@ -2263,8 +2267,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+    <row ht="39.75" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A6" t="s">
         <v>133</v>
       </c>
       <c r="B6" s="23" t="n">
@@ -2587,8 +2591,8 @@
         <v>Under snittet — bæres av de andre</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="19" t="s">
+    <row ht="27" customHeight="true" r="19" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A19" t="s">
         <v>154</v>
       </c>
       <c r="B19" s="19" t="s">
@@ -2643,8 +2647,8 @@
         <v>1216.66666666667</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
+    <row ht="27" customHeight="true" r="24" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A24" t="s">
         <v>159</v>
       </c>
       <c r="B24" s="34" t="n">
@@ -2682,8 +2686,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
+    <row ht="27" customHeight="true" r="28" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A28" t="s">
         <v>164</v>
       </c>
       <c r="B28" s="25" t="n">
@@ -2694,8 +2698,8 @@
         <v>165</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
+    <row ht="27" customHeight="true" r="29" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="40" r="A29" t="s">
         <v>166</v>
       </c>
       <c r="B29" s="25" t="n">
